--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-27).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-10-27).xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -777,28 +777,32 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>736552214</v>
+        <v>430511699</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>418911699</v>
+        <v>430511699</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>230344900</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>317640515</v>
+        <v>320708900</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -1325,10 +1329,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>351115088</v>
+        <v>417771088</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>40</v>
@@ -1343,10 +1347,10 @@
         <v>282976443</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>44428690</v>
+        <v>111084690</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -1359,22 +1363,22 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>38508000</v>
+        <v>77396400</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>38508000</v>
+        <v>77396400</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>38508000</v>
+        <v>77358000</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -1435,22 +1439,22 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>90550292</v>
+        <v>94495292</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>90550292</v>
+        <v>94495292</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>86612607</v>
+        <v>90557607</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -1473,22 +1477,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>65316100</v>
+        <v>70581100</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>65316100</v>
+        <v>70581100</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>61364960</v>
+        <v>66629960</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -1511,22 +1515,22 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>107342366</v>
+        <v>169142604</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>107342366</v>
+        <v>169142604</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>101626500</v>
+        <v>163356250</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -1549,10 +1553,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>108974684</v>
+        <v>98994684</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>4</v>
@@ -1566,11 +1570,15 @@
       <c r="H31" s="6" t="n">
         <v>51881289</v>
       </c>
-      <c r="I31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>9980000</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -1583,22 +1591,22 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>378335637</v>
+        <v>621434137</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>378335637</v>
+        <v>621434137</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>372846417</v>
+        <v>588576917</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -1845,22 +1853,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>132336493</v>
+        <v>145335543</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>132336493</v>
+        <v>145335543</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>123675600</v>
+        <v>136461000</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -2341,10 +2349,10 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>257660249</v>
+        <v>267640249</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
@@ -2367,10 +2375,10 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>257660249</v>
+        <v>267640249</v>
       </c>
     </row>
     <row r="52" ht="45" customHeight="1">
@@ -2996,35 +3004,23 @@
           <t>KECAMATAN PANGKALAN BANTENG - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>4201572</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>4201572</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>4099000</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -3043,40 +3039,36 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
+          <t>KECAMATAN PANGKALAN LADA - 7.01.0.00.0.00.05.0000</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>970303908</v>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="J68" s="10" t="n">
-        <v>970303908</v>
+        <v>14850000</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>14850000</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="45" customHeight="1">
@@ -3085,14 +3077,14 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
+          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>310252566</v>
+        <v>970303908</v>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
@@ -3115,10 +3107,10 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>310252566</v>
+        <v>970303908</v>
       </c>
     </row>
     <row r="70" ht="45" customHeight="1">
@@ -3127,14 +3119,14 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>337845298</v>
+        <v>310252566</v>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
@@ -3157,10 +3149,10 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>337845298</v>
+        <v>310252566</v>
       </c>
     </row>
     <row r="71" ht="45" customHeight="1">
@@ -3169,14 +3161,14 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>304123703</v>
+        <v>337845298</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -3199,10 +3191,10 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>304123703</v>
+        <v>337845298</v>
       </c>
     </row>
     <row r="72" ht="45" customHeight="1">
@@ -3211,14 +3203,14 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>157095572</v>
+        <v>304123703</v>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
@@ -3241,10 +3233,10 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>157095572</v>
+        <v>304123703</v>
       </c>
     </row>
     <row r="73" ht="45" customHeight="1">
@@ -3253,14 +3245,14 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>91017201</v>
+        <v>157095572</v>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
@@ -3283,10 +3275,10 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>91017201</v>
+        <v>157095572</v>
       </c>
     </row>
     <row r="74" ht="45" customHeight="1">
@@ -3295,18 +3287,14 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>91017201</v>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
@@ -3328,15 +3316,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>91017201</v>
       </c>
     </row>
     <row r="75" ht="45" customHeight="1">
@@ -3345,40 +3329,36 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>52763500</v>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>52763500</v>
+        <v>24520790</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>24520790</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>22939000</v>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="45" customHeight="1">
@@ -3387,18 +3367,14 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>52763500</v>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
@@ -3420,15 +3396,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>52763500</v>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1">
@@ -3437,26 +3409,26 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
+          <t>PUSKESMAS ARUT UTARA - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>66380633</v>
+        <v>9036200</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>66380633</v>
+        <v>9036200</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>15724250</v>
+        <v>642500</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -3475,14 +3447,18 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D78" s="10" t="n">
-        <v>496859005</v>
+          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
@@ -3504,11 +3480,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>496859005</v>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="45" customHeight="1">
@@ -3517,40 +3497,36 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>159566746</v>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>159566746</v>
+        <v>66380633</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>66380633</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>15724250</v>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="45" customHeight="1">
@@ -3559,14 +3535,14 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>183754320</v>
+        <v>496859005</v>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
@@ -3589,10 +3565,10 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>183754320</v>
+        <v>496859005</v>
       </c>
     </row>
     <row r="81" ht="45" customHeight="1">
@@ -3601,14 +3577,14 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
+          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>287378738</v>
+        <v>159566746</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3631,10 +3607,10 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>287378738</v>
+        <v>159566746</v>
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
@@ -3643,14 +3619,14 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>196969887</v>
+        <v>183754320</v>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
@@ -3673,10 +3649,10 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>196969887</v>
+        <v>183754320</v>
       </c>
     </row>
     <row r="83" ht="45" customHeight="1">
@@ -3685,14 +3661,14 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>397703689</v>
+        <v>287378738</v>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
@@ -3715,10 +3691,10 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>397703689</v>
+        <v>287378738</v>
       </c>
     </row>
     <row r="84" ht="45" customHeight="1">
@@ -3727,14 +3703,14 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>319912312</v>
+        <v>196969887</v>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
@@ -3757,10 +3733,10 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>319912312</v>
+        <v>196969887</v>
       </c>
     </row>
     <row r="85" ht="45" customHeight="1">
@@ -3769,14 +3745,14 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
+          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>138079030</v>
+        <v>397703689</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -3799,10 +3775,10 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>138079030</v>
+        <v>397703689</v>
       </c>
     </row>
     <row r="86" ht="45" customHeight="1">
@@ -3811,14 +3787,14 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
+          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>411198562</v>
+        <v>319912312</v>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
@@ -3841,10 +3817,10 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>411198562</v>
+        <v>319912312</v>
       </c>
     </row>
     <row r="87" ht="45" customHeight="1">
@@ -3853,14 +3829,14 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>387164122</v>
+        <v>138079030</v>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
@@ -3883,10 +3859,10 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>387164122</v>
+        <v>138079030</v>
       </c>
     </row>
     <row r="88" ht="45" customHeight="1">
@@ -3895,14 +3871,14 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
+          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>289499767</v>
+        <v>411198562</v>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
@@ -3925,10 +3901,10 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>289499767</v>
+        <v>411198562</v>
       </c>
     </row>
     <row r="89" ht="45" customHeight="1">
@@ -3937,14 +3913,14 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
         <v>37</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>346063997</v>
+        <v>387164122</v>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
@@ -3970,7 +3946,7 @@
         <v>37</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>346063997</v>
+        <v>387164122</v>
       </c>
     </row>
     <row r="90" ht="45" customHeight="1">
@@ -3979,14 +3955,14 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>130909625</v>
+        <v>289499767</v>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
@@ -4009,10 +3985,10 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>130909625</v>
+        <v>289499767</v>
       </c>
     </row>
     <row r="91" ht="45" customHeight="1">
@@ -4021,14 +3997,14 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
+          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>186180796</v>
+        <v>346063997</v>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
@@ -4051,10 +4027,10 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>186180796</v>
+        <v>346063997</v>
       </c>
     </row>
     <row r="92" ht="45" customHeight="1">
@@ -4063,14 +4039,14 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>121367900</v>
+        <v>130909625</v>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
@@ -4093,10 +4069,10 @@
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>121367900</v>
+        <v>130909625</v>
       </c>
     </row>
     <row r="93" ht="45" customHeight="1">
@@ -4105,14 +4081,14 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
+          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>368267820</v>
+        <v>186180796</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -4135,10 +4111,10 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>368267820</v>
+        <v>186180796</v>
       </c>
     </row>
     <row r="94" ht="45" customHeight="1">
@@ -4147,14 +4123,14 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
+          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>316118537</v>
+        <v>121367900</v>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
@@ -4177,10 +4153,10 @@
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>316118537</v>
+        <v>121367900</v>
       </c>
     </row>
     <row r="95" ht="45" customHeight="1">
@@ -4189,14 +4165,14 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>179964901</v>
+        <v>368267820</v>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
@@ -4219,10 +4195,10 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>179964901</v>
+        <v>368267820</v>
       </c>
     </row>
     <row r="96" ht="45" customHeight="1">
@@ -4231,36 +4207,40 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
+          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H96" s="10" t="n">
-        <v>26129400</v>
-      </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>316118537</v>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>316118537</v>
       </c>
     </row>
     <row r="97" ht="45" customHeight="1">
@@ -4269,36 +4249,40 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
+          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>158730000</v>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>179964901</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>179964901</v>
       </c>
     </row>
     <row r="98" ht="45" customHeight="1">
@@ -4307,40 +4291,36 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
+          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>294604682</v>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>294604682</v>
+        <v>35716900</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>35716900</v>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>26129400</v>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="45" customHeight="1">
@@ -4349,40 +4329,36 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>529283463</v>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J99" s="6" t="n">
-        <v>529283463</v>
+        <v>108000000</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>158730000</v>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="45" customHeight="1">
@@ -4391,32 +4367,40 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>129198291</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>115323291</v>
-      </c>
-      <c r="G100" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H100" s="10" t="n">
-        <v>113833150</v>
+        <v>294604682</v>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>13875000</v>
+        <v>294604682</v>
       </c>
     </row>
     <row r="101" ht="45" customHeight="1">
@@ -4425,36 +4409,40 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>238180114</v>
-      </c>
-      <c r="E101" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>238180114</v>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>213040407</v>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>529283463</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>529283463</v>
       </c>
     </row>
     <row r="102" ht="45" customHeight="1">
@@ -4463,36 +4451,32 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>419874186</v>
+        <v>129198291</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>419874186</v>
+        <v>115323291</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>414065940</v>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>113833150</v>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>13875000</v>
       </c>
     </row>
     <row r="103" ht="45" customHeight="1">
@@ -4501,40 +4485,36 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>225095700</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="J103" s="6" t="n">
-        <v>225095700</v>
+        <v>238180114</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>238180114</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>213040407</v>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="45" customHeight="1">
@@ -4543,40 +4523,36 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>978880360</v>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>978880360</v>
+        <v>419874186</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>419874186</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>414065940</v>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="45" customHeight="1">
@@ -4585,72 +4561,156 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>225095700</v>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>225095700</v>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>978880360</v>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>978880360</v>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C107" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D107" s="6" t="n">
         <v>1189992706</v>
       </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="n">
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="J105" s="6" t="n">
+      <c r="J107" s="6" t="n">
         <v>1189992706</v>
       </c>
     </row>
-    <row r="106" ht="45" customHeight="1">
-      <c r="A106" s="2" t="inlineStr"/>
-      <c r="B106" s="2" t="inlineStr">
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>3918</v>
-      </c>
-      <c r="D106" s="13" t="n">
-        <v>33813522539</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>557</v>
-      </c>
-      <c r="F106" s="13" t="n">
-        <v>7628867728</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>557</v>
-      </c>
-      <c r="H106" s="13" t="n">
-        <v>6986593893</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>3361</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>26184654811</v>
+      <c r="C108" s="12" t="n">
+        <v>3954</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>33992742774</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>603</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>8059072478</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>603</v>
+      </c>
+      <c r="H108" s="13" t="n">
+        <v>7443694043</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>3351</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>25933670296</v>
       </c>
     </row>
   </sheetData>
@@ -4682,7 +4742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5072,10 +5132,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>803405567</v>
+        <v>585218403</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>7</v>
@@ -5087,13 +5147,13 @@
         <v>7</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>379497000</v>
+        <v>435369000</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>379497000</v>
+        <v>435369000</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -5105,11 +5165,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>218187164</v>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -5856,10 +5920,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1162285000</v>
+        <v>1261203400</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>7</v>
@@ -5890,10 +5954,10 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>195304500</v>
+        <v>294222900</v>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -6226,38 +6290,34 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>4007498984</v>
+        <v>4142498984</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>4007498984</v>
+        <v>4142498984</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>3980863352</v>
+        <v>4115863352</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1475769002</v>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1610769002</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>135000000</v>
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
@@ -6504,10 +6564,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2769384586</v>
+        <v>3136384586</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>23</v>
@@ -6534,10 +6594,10 @@
         <v>100629760</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>95000000</v>
+        <v>462000000</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -6604,42 +6664,34 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>69750000</v>
+        <v>197477500</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>69750000</v>
+        <v>197477500</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>69100000</v>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>196177500</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>127077500</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>127077500</v>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
@@ -7724,10 +7776,10 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1686296362</v>
+        <v>1519296362</v>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
@@ -7770,10 +7822,10 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>1686296362</v>
+        <v>1519296362</v>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
@@ -8382,14 +8434,18 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>461049504</v>
+          <t>KECAMATAN PANGKALAN LADA - 7.01.0.00.0.00.05.0000</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
@@ -8431,11 +8487,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M68" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N68" s="10" t="n">
-        <v>461049504</v>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="45" customHeight="1">
@@ -8444,14 +8504,14 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
+          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>154997000</v>
+        <v>461049504</v>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
@@ -8494,10 +8554,10 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>154997000</v>
+        <v>461049504</v>
       </c>
     </row>
     <row r="70" ht="45" customHeight="1">
@@ -8506,14 +8566,14 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>134864500</v>
+        <v>154997000</v>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
@@ -8556,10 +8616,10 @@
         </is>
       </c>
       <c r="M70" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="10" t="n">
-        <v>134864500</v>
+        <v>154997000</v>
       </c>
     </row>
     <row r="71" ht="45" customHeight="1">
@@ -8568,14 +8628,14 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>332405524</v>
+        <v>134864500</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -8618,10 +8678,10 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>332405524</v>
+        <v>134864500</v>
       </c>
     </row>
     <row r="72" ht="45" customHeight="1">
@@ -8630,14 +8690,14 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>65610832</v>
+        <v>332405524</v>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
@@ -8680,10 +8740,10 @@
         </is>
       </c>
       <c r="M72" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N72" s="10" t="n">
-        <v>65610832</v>
+        <v>332405524</v>
       </c>
     </row>
     <row r="73" ht="45" customHeight="1">
@@ -8692,18 +8752,14 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>65610832</v>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
@@ -8745,15 +8801,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>65610832</v>
       </c>
     </row>
     <row r="74" ht="45" customHeight="1">
@@ -8762,38 +8814,58 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" s="10" t="n">
-        <v>301830114</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" s="10" t="n">
-        <v>301830114</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" s="10" t="n">
-        <v>68020787</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v>68020787</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="10" t="n">
-        <v>65401200</v>
+          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
@@ -8812,60 +8884,48 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>258006238</v>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="n">
+        <v>301830114</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N75" s="6" t="n">
-        <v>258006238</v>
+      <c r="F75" s="6" t="n">
+        <v>301830114</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>68020787</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>68020787</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>65401200</v>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="45" customHeight="1">
@@ -8874,32 +8934,44 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>153891630</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="10" t="n">
-        <v>153891630</v>
-      </c>
-      <c r="G76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="10" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="I76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>53835000</v>
+        <v>258006238</v>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
         <is>
@@ -8911,15 +8983,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M76" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N76" s="10" t="n">
+        <v>258006238</v>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1">
@@ -8928,7 +8996,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
+          <t>PUSKESMAS ARUT UTARA - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -8998,44 +9066,32 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
+          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>420784548</v>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>153891630</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>153891630</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>53835000</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>53835000</v>
       </c>
       <c r="K78" s="11" t="inlineStr">
         <is>
@@ -9047,11 +9103,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M78" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N78" s="10" t="n">
-        <v>420784548</v>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="45" customHeight="1">
@@ -9060,14 +9120,18 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>196677985</v>
+          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
@@ -9109,11 +9173,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N79" s="6" t="n">
-        <v>196677985</v>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="45" customHeight="1">
@@ -9122,14 +9190,14 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>154700000</v>
+        <v>420784548</v>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
@@ -9172,10 +9240,10 @@
         </is>
       </c>
       <c r="M80" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>154700000</v>
+        <v>420784548</v>
       </c>
     </row>
     <row r="81" ht="45" customHeight="1">
@@ -9184,14 +9252,14 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
+          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>717939851</v>
+        <v>196677985</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -9234,10 +9302,10 @@
         </is>
       </c>
       <c r="M81" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>717939851</v>
+        <v>196677985</v>
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
@@ -9246,14 +9314,14 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>145950000</v>
+        <v>154700000</v>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
@@ -9299,7 +9367,7 @@
         <v>2</v>
       </c>
       <c r="N82" s="10" t="n">
-        <v>145950000</v>
+        <v>154700000</v>
       </c>
     </row>
     <row r="83" ht="45" customHeight="1">
@@ -9308,14 +9376,14 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>494958640</v>
+        <v>717939851</v>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
@@ -9358,10 +9426,10 @@
         </is>
       </c>
       <c r="M83" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>494958640</v>
+        <v>717939851</v>
       </c>
     </row>
     <row r="84" ht="45" customHeight="1">
@@ -9370,14 +9438,14 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>189350000</v>
+        <v>145950000</v>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
@@ -9423,7 +9491,7 @@
         <v>2</v>
       </c>
       <c r="N84" s="10" t="n">
-        <v>189350000</v>
+        <v>145950000</v>
       </c>
     </row>
     <row r="85" ht="45" customHeight="1">
@@ -9432,14 +9500,14 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
+          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>235342500</v>
+        <v>494958640</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -9482,10 +9550,10 @@
         </is>
       </c>
       <c r="M85" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>235342500</v>
+        <v>494958640</v>
       </c>
     </row>
     <row r="86" ht="45" customHeight="1">
@@ -9494,14 +9562,14 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
+          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>141393225</v>
+        <v>189350000</v>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
@@ -9547,7 +9615,7 @@
         <v>2</v>
       </c>
       <c r="N86" s="10" t="n">
-        <v>141393225</v>
+        <v>189350000</v>
       </c>
     </row>
     <row r="87" ht="45" customHeight="1">
@@ -9556,14 +9624,14 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>194600000</v>
+        <v>235342500</v>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
@@ -9606,10 +9674,10 @@
         </is>
       </c>
       <c r="M87" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>194600000</v>
+        <v>235342500</v>
       </c>
     </row>
     <row r="88" ht="45" customHeight="1">
@@ -9618,18 +9686,14 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
-        </is>
-      </c>
-      <c r="C88" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>141393225</v>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
@@ -9671,15 +9735,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M88" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M88" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" s="10" t="n">
+        <v>141393225</v>
       </c>
     </row>
     <row r="89" ht="45" customHeight="1">
@@ -9688,14 +9748,14 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>189000000</v>
+        <v>194600000</v>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
@@ -9738,10 +9798,10 @@
         </is>
       </c>
       <c r="M89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>189000000</v>
+        <v>194600000</v>
       </c>
     </row>
     <row r="90" ht="45" customHeight="1">
@@ -9750,7 +9810,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
@@ -9820,14 +9880,14 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
+          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>143150000</v>
+        <v>189000000</v>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
@@ -9870,10 +9930,10 @@
         </is>
       </c>
       <c r="M91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>143150000</v>
+        <v>189000000</v>
       </c>
     </row>
     <row r="92" ht="45" customHeight="1">
@@ -9882,14 +9942,18 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="10" t="n">
-        <v>149292000</v>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
@@ -9931,11 +9995,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M92" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N92" s="10" t="n">
-        <v>149292000</v>
+      <c r="M92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="45" customHeight="1">
@@ -9944,14 +10012,14 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
+          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>275450000</v>
+        <v>143150000</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -9994,10 +10062,10 @@
         </is>
       </c>
       <c r="M93" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>275450000</v>
+        <v>143150000</v>
       </c>
     </row>
     <row r="94" ht="45" customHeight="1">
@@ -10006,14 +10074,14 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
+          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>159397453</v>
+        <v>149292000</v>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
@@ -10056,10 +10124,10 @@
         </is>
       </c>
       <c r="M94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N94" s="10" t="n">
-        <v>159397453</v>
+        <v>149292000</v>
       </c>
     </row>
     <row r="95" ht="45" customHeight="1">
@@ -10068,14 +10136,14 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>175130000</v>
+        <v>275450000</v>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
@@ -10118,10 +10186,10 @@
         </is>
       </c>
       <c r="M95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N95" s="6" t="n">
-        <v>175130000</v>
+        <v>275450000</v>
       </c>
     </row>
     <row r="96" ht="45" customHeight="1">
@@ -10130,32 +10198,44 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
+          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="10" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="10" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="I96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>43541637</v>
+        <v>159397453</v>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K96" s="11" t="inlineStr">
         <is>
@@ -10167,15 +10247,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M96" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M96" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N96" s="10" t="n">
+        <v>159397453</v>
       </c>
     </row>
     <row r="97" ht="45" customHeight="1">
@@ -10184,32 +10260,44 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
+          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>49950000</v>
+        <v>175130000</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
@@ -10221,15 +10309,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M97" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" s="6" t="n">
+        <v>175130000</v>
       </c>
     </row>
     <row r="98" ht="45" customHeight="1">
@@ -10238,44 +10322,32 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
+          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>276471012</v>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>146817603</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>146817603</v>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="I98" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>43541637</v>
       </c>
       <c r="K98" s="11" t="inlineStr">
         <is>
@@ -10287,11 +10359,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M98" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N98" s="10" t="n">
-        <v>276471012</v>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="45" customHeight="1">
@@ -10300,44 +10376,32 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>3503487490</v>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50400000</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>49950000</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
@@ -10349,11 +10413,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M99" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N99" s="6" t="n">
-        <v>3503487490</v>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="45" customHeight="1">
@@ -10362,32 +10430,44 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>205350000</v>
-      </c>
-      <c r="E100" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>55500000</v>
-      </c>
-      <c r="G100" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="10" t="n">
-        <v>55100000</v>
-      </c>
-      <c r="I100" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>55100000</v>
+        <v>276471012</v>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K100" s="11" t="inlineStr">
         <is>
@@ -10400,10 +10480,10 @@
         </is>
       </c>
       <c r="M100" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N100" s="10" t="n">
-        <v>149850000</v>
+        <v>276471012</v>
       </c>
     </row>
     <row r="101" ht="45" customHeight="1">
@@ -10412,32 +10492,44 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>639698247</v>
-      </c>
-      <c r="E101" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>564698247</v>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>552004825</v>
-      </c>
-      <c r="I101" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>552004825</v>
+        <v>3503487490</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
@@ -10450,10 +10542,10 @@
         </is>
       </c>
       <c r="M101" s="4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>75000000</v>
+        <v>3503487490</v>
       </c>
     </row>
     <row r="102" ht="45" customHeight="1">
@@ -10462,32 +10554,32 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>1415832056</v>
+        <v>205350000</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>1415832056</v>
+        <v>55500000</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n">
-        <v>1411155433</v>
+        <v>55100000</v>
       </c>
       <c r="I102" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>1282055107</v>
+        <v>55100000</v>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
@@ -10499,15 +10591,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M102" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N102" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M102" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="10" t="n">
+        <v>149850000</v>
       </c>
     </row>
     <row r="103" ht="45" customHeight="1">
@@ -10516,44 +10604,32 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>257652876</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>639698247</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>564698247</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>552004825</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>552004825</v>
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
@@ -10566,10 +10642,10 @@
         </is>
       </c>
       <c r="M103" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>257652876</v>
+        <v>75000000</v>
       </c>
     </row>
     <row r="104" ht="45" customHeight="1">
@@ -10578,44 +10654,32 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>1306540170</v>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1415832056</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>1415832056</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>1411155433</v>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>1282055107</v>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
@@ -10627,11 +10691,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N104" s="10" t="n">
-        <v>1306540170</v>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="45" customHeight="1">
@@ -10640,104 +10708,228 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>257652876</v>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N105" s="6" t="n">
+        <v>257652876</v>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>1306540170</v>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" s="10" t="n">
+        <v>1306540170</v>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C107" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D107" s="6" t="n">
         <v>2761955482</v>
       </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" s="4" t="n">
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="N105" s="6" t="n">
+      <c r="N107" s="6" t="n">
         <v>2761955482</v>
       </c>
     </row>
-    <row r="106" ht="45" customHeight="1">
-      <c r="A106" s="2" t="inlineStr"/>
-      <c r="B106" s="2" t="inlineStr">
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>885</v>
-      </c>
-      <c r="D106" s="13" t="n">
-        <v>104630750358</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>527</v>
-      </c>
-      <c r="F106" s="13" t="n">
-        <v>66270013213</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>527</v>
-      </c>
-      <c r="H106" s="13" t="n">
-        <v>64402379552</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>383</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>48322576553</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L106" s="13" t="n">
-        <v>1796394590</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>358</v>
-      </c>
-      <c r="N106" s="13" t="n">
-        <v>38360737145</v>
+      <c r="C108" s="12" t="n">
+        <v>887</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>104974209094</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>66532740713</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="H108" s="13" t="n">
+        <v>64720329052</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>386</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>48640526053</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>2058472090</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>357</v>
+      </c>
+      <c r="N108" s="13" t="n">
+        <v>38441468381</v>
       </c>
     </row>
   </sheetData>
@@ -10769,7 +10961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12202,13 +12394,13 @@
         <v>46</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>34664094970</v>
+        <v>34663064970</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>42</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>33657050970</v>
+        <v>33656020970</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -12489,38 +12681,34 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>1305858000</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1305858000</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>1303419000</v>
+      </c>
+      <c r="I32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>1103338000</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>1103338000</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="10" t="n">
-        <v>1100899000</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="J32" s="10" t="n">
-        <v>711399000</v>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>913919000</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>202520000</v>
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
@@ -14737,7 +14925,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
+          <t>KECAMATAN PANGKALAN LADA - 7.01.0.00.0.00.05.0000</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -14807,7 +14995,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
+          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -14877,7 +15065,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -14947,7 +15135,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -15017,7 +15205,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -15087,7 +15275,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -15157,7 +15345,7 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
+          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -15227,14 +15415,18 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>2122245491</v>
+          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
@@ -15276,11 +15468,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" s="6" t="n">
-        <v>2122245491</v>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="45" customHeight="1">
@@ -15289,18 +15485,14 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>2122245491</v>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
@@ -15342,15 +15534,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M76" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" s="10" t="n">
+        <v>2122245491</v>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1">
@@ -15359,7 +15547,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
+          <t>PUSKESMAS ARUT UTARA - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -15429,14 +15617,18 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="10" t="n">
-        <v>1032660852</v>
+          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
@@ -15478,11 +15670,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M78" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" s="10" t="n">
-        <v>1032660852</v>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="45" customHeight="1">
@@ -15491,7 +15687,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -15561,18 +15757,14 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>1032660852</v>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
@@ -15614,15 +15806,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="10" t="n">
+        <v>1032660852</v>
       </c>
     </row>
     <row r="81" ht="45" customHeight="1">
@@ -15631,14 +15819,18 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="6" t="n">
-        <v>217174472</v>
+          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -15680,11 +15872,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" s="6" t="n">
-        <v>217174472</v>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="45" customHeight="1">
@@ -15693,7 +15889,7 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -15763,14 +15959,14 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>223700000</v>
+        <v>217174472</v>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
@@ -15816,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>223700000</v>
+        <v>217174472</v>
       </c>
     </row>
     <row r="84" ht="45" customHeight="1">
@@ -15825,7 +16021,7 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
@@ -15895,18 +16091,14 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>223700000</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -15948,15 +16140,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>223700000</v>
       </c>
     </row>
     <row r="86" ht="45" customHeight="1">
@@ -15965,7 +16153,7 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
+          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
@@ -16035,7 +16223,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -16105,7 +16293,7 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
+          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
@@ -16175,7 +16363,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -16245,7 +16433,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
@@ -16315,7 +16503,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
+          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -16385,7 +16573,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -16455,7 +16643,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
+          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -16525,7 +16713,7 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
+          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
@@ -16595,7 +16783,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -16665,7 +16853,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
+          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
@@ -16735,38 +16923,58 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>8054692000</v>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>8054692000</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>2808340212</v>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>2808340212</v>
-      </c>
-      <c r="K97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="6" t="n">
-        <v>64551162</v>
+          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
@@ -16785,7 +16993,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
+          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
@@ -16855,60 +17063,48 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>6344106637</v>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="N99" s="6" t="n">
-        <v>6344106637</v>
+        <v>8054692000</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>8054692000</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>2808340212</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>2808340212</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" s="6" t="n">
+        <v>64551162</v>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="45" customHeight="1">
@@ -16917,7 +17113,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
@@ -16987,32 +17183,44 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>3294207800</v>
-      </c>
-      <c r="E101" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F101" s="6" t="n">
-        <v>3294207800</v>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H101" s="6" t="n">
-        <v>3091941500</v>
-      </c>
-      <c r="I101" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>2207941500</v>
+        <v>6344106637</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
@@ -17024,15 +17232,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M101" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N101" s="6" t="n">
+        <v>6344106637</v>
       </c>
     </row>
     <row r="102" ht="45" customHeight="1">
@@ -17041,32 +17245,48 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D102" s="10" t="n">
-        <v>3947239961</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>3947239961</v>
-      </c>
-      <c r="G102" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H102" s="10" t="n">
-        <v>3847376000</v>
-      </c>
-      <c r="I102" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>3847376000</v>
+          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K102" s="11" t="inlineStr">
         <is>
@@ -17095,44 +17315,32 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>211404000</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3294207800</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>3294207800</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>3091941500</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J103" s="6" t="n">
+        <v>2207941500</v>
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
@@ -17144,11 +17352,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" s="6" t="n">
-        <v>211404000</v>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="45" customHeight="1">
@@ -17157,44 +17369,32 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>264251856</v>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3947239961</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>3947239961</v>
+      </c>
+      <c r="G104" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>3847376000</v>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>3847376000</v>
       </c>
       <c r="K104" s="11" t="inlineStr">
         <is>
@@ -17206,11 +17406,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N104" s="10" t="n">
-        <v>264251856</v>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="45" customHeight="1">
@@ -17219,103 +17423,227 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>211404000</v>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="6" t="n">
+        <v>211404000</v>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>264251856</v>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="10" t="n">
+        <v>264251856</v>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D107" s="6" t="n">
         <v>3838859800</v>
       </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" s="4" t="n">
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="N105" s="6" t="n">
+      <c r="N107" s="6" t="n">
         <v>3838859800</v>
       </c>
     </row>
-    <row r="106" ht="45" customHeight="1">
-      <c r="A106" s="2" t="inlineStr"/>
-      <c r="B106" s="2" t="inlineStr">
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>239</v>
-      </c>
-      <c r="D106" s="13" t="n">
-        <v>181361828470</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="F106" s="13" t="n">
-        <v>147176925531</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="H106" s="13" t="n">
-        <v>71920708305</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>68573298305</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="L106" s="13" t="n">
-        <v>4430709261</v>
-      </c>
-      <c r="M106" s="12" t="n">
+      <c r="C108" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>181564348470</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>163</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>147379445531</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>163</v>
+      </c>
+      <c r="H108" s="13" t="n">
+        <v>72122198305</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>68774788305</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>4633229261</v>
+      </c>
+      <c r="M108" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="N106" s="13" t="n">
+      <c r="N108" s="13" t="n">
         <v>34184902939</v>
       </c>
     </row>
@@ -17348,7 +17676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19377,13 +19705,13 @@
         <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>2688000000</v>
+        <v>2646500000</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2688000000</v>
+        <v>2646500000</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>1</v>
@@ -21632,7 +21960,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
+          <t>KECAMATAN PANGKALAN LADA - 7.01.0.00.0.00.05.0000</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -21702,7 +22030,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
+          <t>Kecamatan Arut Selatan - 7.01.0.00.0.00.02.0000</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -21772,7 +22100,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
+          <t>Kecamatan Arut Utara - 7.01.0.00.0.00.04.0000</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -21842,7 +22170,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
+          <t>Kecamatan Kotawaringin Lama - 7.01.0.00.0.00.03.0000</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -21912,7 +22240,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
+          <t>Kecamatan Kumai - 7.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -21982,7 +22310,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
+          <t>Kecamatan Pangkalan Banteng - 7.01.0.00.0.00.06.0000</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -22052,7 +22380,7 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
+          <t>Kecamatan Pangkalan Lada - 7.01.0.00.0.00.05.0000</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -22122,7 +22450,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
+          <t>LABORATORIUM KESEHATAN DAERAH - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -22192,7 +22520,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
+          <t>Laboratorium Kesehatan Daerah - 1.02.0.00.0.00.01.0003</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -22262,7 +22590,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
+          <t>PUSKESMAS ARUT UTARA - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -22332,7 +22660,7 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
+          <t>PUSKESMAS NATAI PELINGKAU - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -22402,7 +22730,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
+          <t>PUSKESMAS RIAM DURIAN - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -22472,7 +22800,7 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
+          <t>Puskesmas Arut Selatan - 1.02.0.00.0.00.01.0004</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
@@ -22542,7 +22870,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
+          <t>Puskesmas Arut Utara - 1.02.0.00.0.00.01.0017</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -22612,7 +22940,7 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
+          <t>Puskesmas Ipuh Bangun Jaya - 1.02.0.00.0.00.01.0021</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
@@ -22682,7 +23010,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
+          <t>Puskesmas Karang Mulya - 1.02.0.00.0.00.01.0016</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -22752,7 +23080,7 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
+          <t>Puskesmas Kotawaringin Lama - 1.02.0.00.0.00.01.0019</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
@@ -22822,7 +23150,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
+          <t>Puskesmas Kumai - 1.02.0.00.0.00.01.0010</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -22892,7 +23220,7 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
+          <t>Puskesmas Kumpai Batu Atas - 1.02.0.00.0.00.01.0008</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
@@ -22962,7 +23290,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
+          <t>Puskesmas Madurejo - 1.02.0.00.0.00.01.0005</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
@@ -23032,7 +23360,7 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
+          <t>Puskesmas Mendawai - 1.02.0.00.0.00.01.0006</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
@@ -23102,7 +23430,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
+          <t>Puskesmas Natai Pelingkau - 1.02.0.00.0.00.01.0007</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -23172,7 +23500,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
+          <t>Puskesmas Pandu Sanjaya - 1.02.0.00.0.00.01.0014</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
@@ -23242,7 +23570,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
+          <t>Puskesmas Pangkalan Lada - 1.02.0.00.0.00.01.0013</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -23312,7 +23640,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
+          <t>Puskesmas Riam Durian - 1.02.0.00.0.00.01.0020</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -23382,7 +23710,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
+          <t>Puskesmas Runtu - 1.02.0.00.0.00.01.0009</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
@@ -23452,7 +23780,7 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
+          <t>Puskesmas Sambi - 1.02.0.00.0.00.01.0018</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
@@ -23522,7 +23850,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+          <t>Puskesmas Semanggang - 1.02.0.00.0.00.01.0015</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -23592,7 +23920,7 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
+          <t>Puskesmas Sungai Rangit - 1.02.0.00.0.00.01.0012</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
@@ -23662,32 +23990,48 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>83360000000</v>
-      </c>
-      <c r="E97" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F97" s="6" t="n">
-        <v>83360000000</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H97" s="6" t="n">
-        <v>8336802274</v>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>8336802274</v>
+          <t>Puskesmas Teluk Bogam - 1.02.0.00.0.00.01.0011</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
@@ -23716,7 +24060,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
+          <t>RUMAH SAKIT KUTARINGIN - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
@@ -23786,44 +24130,32 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+          <t>RUMAH SAKIT UMUM DAERAH SULTAN IMANUDDIN - 1.02.0.00.0.00.01.0001</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>70337180038</v>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>83360000000</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>83360000000</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>8336802274</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>8336802274</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
@@ -23835,11 +24167,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M99" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N99" s="6" t="n">
-        <v>70337180038</v>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="45" customHeight="1">
@@ -23848,7 +24184,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
+          <t>Rumah Sakit Kutaringin - 1.02.0.00.0.00.01.0002</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
@@ -23918,18 +24254,14 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin - 1.02.0.00.0.00.01.0001</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>70337180038</v>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
@@ -23971,15 +24303,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N101" s="6" t="n">
+        <v>70337180038</v>
       </c>
     </row>
     <row r="102" ht="45" customHeight="1">
@@ -23988,7 +24316,7 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SATUAN POLISI PAMONG PRAJA - 1.05.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
@@ -24058,7 +24386,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DAERAH - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -24128,7 +24456,7 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+          <t>SEKRETARIAT DPRD - 4.02.0.00.0.00.01.0000</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
@@ -24198,115 +24526,255 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
+          <t>Satuan Polisi Pamong Praja - 1.05.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="45" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Sekretariat DPRD - 4.02.0.00.0.00.01.0000</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="45" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
           <t>Sekretariat Daerah - 4.01.0.00.0.00.01.0000</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="45" customHeight="1">
-      <c r="A106" s="2" t="inlineStr"/>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C108" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="D106" s="13" t="n">
-        <v>248425975553</v>
-      </c>
-      <c r="E106" s="12" t="n">
+      <c r="D108" s="13" t="n">
+        <v>248384475553</v>
+      </c>
+      <c r="E108" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F106" s="13" t="n">
-        <v>147115370800</v>
-      </c>
-      <c r="G106" s="12" t="n">
+      <c r="F108" s="13" t="n">
+        <v>147073870800</v>
+      </c>
+      <c r="G108" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H106" s="13" t="n">
+      <c r="H108" s="13" t="n">
         <v>71235380009</v>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="I108" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J106" s="13" t="n">
+      <c r="J108" s="13" t="n">
         <v>71235380009</v>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M106" s="12" t="n">
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N106" s="13" t="n">
+      <c r="N108" s="13" t="n">
         <v>101310604753</v>
       </c>
     </row>
